--- a/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/hxprofit/HXProfit.xlsx
+++ b/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/hxprofit/HXProfit.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20373"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4487337E-27DE-4803-B5D6-DE6DB5537634}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC589F52-ED90-47EE-B8CB-E880C0ECE4AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,12 +12,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>项目</t>
   </si>
@@ -97,24 +97,6 @@
     <t>三、营业利润</t>
   </si>
   <si>
-    <t>${dto.bq.operProfit}</t>
-  </si>
-  <si>
-    <t>${dto.bn.operProfit}</t>
-  </si>
-  <si>
-    <t>${dto.sy.operProfit}</t>
-  </si>
-  <si>
-    <t>${entity.busiIncBQ}</t>
-  </si>
-  <si>
-    <t>${entity.busiIncSY}</t>
-  </si>
-  <si>
-    <t>${entity.busiIncBN}</t>
-  </si>
-  <si>
     <t>${entity.bq.lixiInc}</t>
   </si>
   <si>
@@ -212,15 +194,6 @@
   </si>
   <si>
     <t>${entity.bn.exchInc}</t>
-  </si>
-  <si>
-    <t>${entity.busiPayBQ}</t>
-  </si>
-  <si>
-    <t>${entity.busiPaySY}</t>
-  </si>
-  <si>
-    <t>${entity.busiPayBN}</t>
   </si>
   <si>
     <t>${entity.bq.prodPay}</t>
@@ -397,7 +370,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -425,6 +398,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -767,265 +743,329 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="35.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="27" style="2" customWidth="1"/>
-    <col min="4" max="256" width="11" style="1"/>
-    <col min="257" max="257" width="35.125" style="1" customWidth="1"/>
-    <col min="258" max="258" width="33.375" style="1" customWidth="1"/>
-    <col min="259" max="259" width="27" style="1" customWidth="1"/>
-    <col min="260" max="512" width="11" style="1"/>
-    <col min="513" max="513" width="35.125" style="1" customWidth="1"/>
-    <col min="514" max="514" width="33.375" style="1" customWidth="1"/>
-    <col min="515" max="515" width="27" style="1" customWidth="1"/>
-    <col min="516" max="768" width="11" style="1"/>
-    <col min="769" max="769" width="35.125" style="1" customWidth="1"/>
-    <col min="770" max="770" width="33.375" style="1" customWidth="1"/>
-    <col min="771" max="771" width="27" style="1" customWidth="1"/>
-    <col min="772" max="1024" width="11" style="1"/>
-    <col min="1025" max="1025" width="35.125" style="1" customWidth="1"/>
-    <col min="1026" max="1026" width="33.375" style="1" customWidth="1"/>
-    <col min="1027" max="1027" width="27" style="1" customWidth="1"/>
-    <col min="1028" max="1280" width="11" style="1"/>
-    <col min="1281" max="1281" width="35.125" style="1" customWidth="1"/>
-    <col min="1282" max="1282" width="33.375" style="1" customWidth="1"/>
-    <col min="1283" max="1283" width="27" style="1" customWidth="1"/>
-    <col min="1284" max="1536" width="11" style="1"/>
-    <col min="1537" max="1537" width="35.125" style="1" customWidth="1"/>
-    <col min="1538" max="1538" width="33.375" style="1" customWidth="1"/>
-    <col min="1539" max="1539" width="27" style="1" customWidth="1"/>
-    <col min="1540" max="1792" width="11" style="1"/>
-    <col min="1793" max="1793" width="35.125" style="1" customWidth="1"/>
-    <col min="1794" max="1794" width="33.375" style="1" customWidth="1"/>
-    <col min="1795" max="1795" width="27" style="1" customWidth="1"/>
-    <col min="1796" max="2048" width="11" style="1"/>
-    <col min="2049" max="2049" width="35.125" style="1" customWidth="1"/>
-    <col min="2050" max="2050" width="33.375" style="1" customWidth="1"/>
-    <col min="2051" max="2051" width="27" style="1" customWidth="1"/>
-    <col min="2052" max="2304" width="11" style="1"/>
-    <col min="2305" max="2305" width="35.125" style="1" customWidth="1"/>
-    <col min="2306" max="2306" width="33.375" style="1" customWidth="1"/>
-    <col min="2307" max="2307" width="27" style="1" customWidth="1"/>
-    <col min="2308" max="2560" width="11" style="1"/>
-    <col min="2561" max="2561" width="35.125" style="1" customWidth="1"/>
-    <col min="2562" max="2562" width="33.375" style="1" customWidth="1"/>
-    <col min="2563" max="2563" width="27" style="1" customWidth="1"/>
-    <col min="2564" max="2816" width="11" style="1"/>
-    <col min="2817" max="2817" width="35.125" style="1" customWidth="1"/>
-    <col min="2818" max="2818" width="33.375" style="1" customWidth="1"/>
-    <col min="2819" max="2819" width="27" style="1" customWidth="1"/>
-    <col min="2820" max="3072" width="11" style="1"/>
-    <col min="3073" max="3073" width="35.125" style="1" customWidth="1"/>
-    <col min="3074" max="3074" width="33.375" style="1" customWidth="1"/>
-    <col min="3075" max="3075" width="27" style="1" customWidth="1"/>
-    <col min="3076" max="3328" width="11" style="1"/>
-    <col min="3329" max="3329" width="35.125" style="1" customWidth="1"/>
-    <col min="3330" max="3330" width="33.375" style="1" customWidth="1"/>
-    <col min="3331" max="3331" width="27" style="1" customWidth="1"/>
-    <col min="3332" max="3584" width="11" style="1"/>
-    <col min="3585" max="3585" width="35.125" style="1" customWidth="1"/>
-    <col min="3586" max="3586" width="33.375" style="1" customWidth="1"/>
-    <col min="3587" max="3587" width="27" style="1" customWidth="1"/>
-    <col min="3588" max="3840" width="11" style="1"/>
-    <col min="3841" max="3841" width="35.125" style="1" customWidth="1"/>
-    <col min="3842" max="3842" width="33.375" style="1" customWidth="1"/>
-    <col min="3843" max="3843" width="27" style="1" customWidth="1"/>
-    <col min="3844" max="4096" width="11" style="1"/>
-    <col min="4097" max="4097" width="35.125" style="1" customWidth="1"/>
-    <col min="4098" max="4098" width="33.375" style="1" customWidth="1"/>
-    <col min="4099" max="4099" width="27" style="1" customWidth="1"/>
-    <col min="4100" max="4352" width="11" style="1"/>
-    <col min="4353" max="4353" width="35.125" style="1" customWidth="1"/>
-    <col min="4354" max="4354" width="33.375" style="1" customWidth="1"/>
-    <col min="4355" max="4355" width="27" style="1" customWidth="1"/>
-    <col min="4356" max="4608" width="11" style="1"/>
-    <col min="4609" max="4609" width="35.125" style="1" customWidth="1"/>
-    <col min="4610" max="4610" width="33.375" style="1" customWidth="1"/>
-    <col min="4611" max="4611" width="27" style="1" customWidth="1"/>
-    <col min="4612" max="4864" width="11" style="1"/>
-    <col min="4865" max="4865" width="35.125" style="1" customWidth="1"/>
-    <col min="4866" max="4866" width="33.375" style="1" customWidth="1"/>
-    <col min="4867" max="4867" width="27" style="1" customWidth="1"/>
-    <col min="4868" max="5120" width="11" style="1"/>
-    <col min="5121" max="5121" width="35.125" style="1" customWidth="1"/>
-    <col min="5122" max="5122" width="33.375" style="1" customWidth="1"/>
-    <col min="5123" max="5123" width="27" style="1" customWidth="1"/>
-    <col min="5124" max="5376" width="11" style="1"/>
-    <col min="5377" max="5377" width="35.125" style="1" customWidth="1"/>
-    <col min="5378" max="5378" width="33.375" style="1" customWidth="1"/>
-    <col min="5379" max="5379" width="27" style="1" customWidth="1"/>
-    <col min="5380" max="5632" width="11" style="1"/>
-    <col min="5633" max="5633" width="35.125" style="1" customWidth="1"/>
-    <col min="5634" max="5634" width="33.375" style="1" customWidth="1"/>
-    <col min="5635" max="5635" width="27" style="1" customWidth="1"/>
-    <col min="5636" max="5888" width="11" style="1"/>
-    <col min="5889" max="5889" width="35.125" style="1" customWidth="1"/>
-    <col min="5890" max="5890" width="33.375" style="1" customWidth="1"/>
-    <col min="5891" max="5891" width="27" style="1" customWidth="1"/>
-    <col min="5892" max="6144" width="11" style="1"/>
-    <col min="6145" max="6145" width="35.125" style="1" customWidth="1"/>
-    <col min="6146" max="6146" width="33.375" style="1" customWidth="1"/>
-    <col min="6147" max="6147" width="27" style="1" customWidth="1"/>
-    <col min="6148" max="6400" width="11" style="1"/>
-    <col min="6401" max="6401" width="35.125" style="1" customWidth="1"/>
-    <col min="6402" max="6402" width="33.375" style="1" customWidth="1"/>
-    <col min="6403" max="6403" width="27" style="1" customWidth="1"/>
-    <col min="6404" max="6656" width="11" style="1"/>
-    <col min="6657" max="6657" width="35.125" style="1" customWidth="1"/>
-    <col min="6658" max="6658" width="33.375" style="1" customWidth="1"/>
-    <col min="6659" max="6659" width="27" style="1" customWidth="1"/>
-    <col min="6660" max="6912" width="11" style="1"/>
-    <col min="6913" max="6913" width="35.125" style="1" customWidth="1"/>
-    <col min="6914" max="6914" width="33.375" style="1" customWidth="1"/>
-    <col min="6915" max="6915" width="27" style="1" customWidth="1"/>
-    <col min="6916" max="7168" width="11" style="1"/>
-    <col min="7169" max="7169" width="35.125" style="1" customWidth="1"/>
-    <col min="7170" max="7170" width="33.375" style="1" customWidth="1"/>
-    <col min="7171" max="7171" width="27" style="1" customWidth="1"/>
-    <col min="7172" max="7424" width="11" style="1"/>
-    <col min="7425" max="7425" width="35.125" style="1" customWidth="1"/>
-    <col min="7426" max="7426" width="33.375" style="1" customWidth="1"/>
-    <col min="7427" max="7427" width="27" style="1" customWidth="1"/>
-    <col min="7428" max="7680" width="11" style="1"/>
-    <col min="7681" max="7681" width="35.125" style="1" customWidth="1"/>
-    <col min="7682" max="7682" width="33.375" style="1" customWidth="1"/>
-    <col min="7683" max="7683" width="27" style="1" customWidth="1"/>
-    <col min="7684" max="7936" width="11" style="1"/>
-    <col min="7937" max="7937" width="35.125" style="1" customWidth="1"/>
-    <col min="7938" max="7938" width="33.375" style="1" customWidth="1"/>
-    <col min="7939" max="7939" width="27" style="1" customWidth="1"/>
-    <col min="7940" max="8192" width="11" style="1"/>
-    <col min="8193" max="8193" width="35.125" style="1" customWidth="1"/>
-    <col min="8194" max="8194" width="33.375" style="1" customWidth="1"/>
-    <col min="8195" max="8195" width="27" style="1" customWidth="1"/>
-    <col min="8196" max="8448" width="11" style="1"/>
-    <col min="8449" max="8449" width="35.125" style="1" customWidth="1"/>
-    <col min="8450" max="8450" width="33.375" style="1" customWidth="1"/>
-    <col min="8451" max="8451" width="27" style="1" customWidth="1"/>
-    <col min="8452" max="8704" width="11" style="1"/>
-    <col min="8705" max="8705" width="35.125" style="1" customWidth="1"/>
-    <col min="8706" max="8706" width="33.375" style="1" customWidth="1"/>
-    <col min="8707" max="8707" width="27" style="1" customWidth="1"/>
-    <col min="8708" max="8960" width="11" style="1"/>
-    <col min="8961" max="8961" width="35.125" style="1" customWidth="1"/>
-    <col min="8962" max="8962" width="33.375" style="1" customWidth="1"/>
-    <col min="8963" max="8963" width="27" style="1" customWidth="1"/>
-    <col min="8964" max="9216" width="11" style="1"/>
-    <col min="9217" max="9217" width="35.125" style="1" customWidth="1"/>
-    <col min="9218" max="9218" width="33.375" style="1" customWidth="1"/>
-    <col min="9219" max="9219" width="27" style="1" customWidth="1"/>
-    <col min="9220" max="9472" width="11" style="1"/>
-    <col min="9473" max="9473" width="35.125" style="1" customWidth="1"/>
-    <col min="9474" max="9474" width="33.375" style="1" customWidth="1"/>
-    <col min="9475" max="9475" width="27" style="1" customWidth="1"/>
-    <col min="9476" max="9728" width="11" style="1"/>
-    <col min="9729" max="9729" width="35.125" style="1" customWidth="1"/>
-    <col min="9730" max="9730" width="33.375" style="1" customWidth="1"/>
-    <col min="9731" max="9731" width="27" style="1" customWidth="1"/>
-    <col min="9732" max="9984" width="11" style="1"/>
-    <col min="9985" max="9985" width="35.125" style="1" customWidth="1"/>
-    <col min="9986" max="9986" width="33.375" style="1" customWidth="1"/>
-    <col min="9987" max="9987" width="27" style="1" customWidth="1"/>
-    <col min="9988" max="10240" width="11" style="1"/>
-    <col min="10241" max="10241" width="35.125" style="1" customWidth="1"/>
-    <col min="10242" max="10242" width="33.375" style="1" customWidth="1"/>
-    <col min="10243" max="10243" width="27" style="1" customWidth="1"/>
-    <col min="10244" max="10496" width="11" style="1"/>
-    <col min="10497" max="10497" width="35.125" style="1" customWidth="1"/>
-    <col min="10498" max="10498" width="33.375" style="1" customWidth="1"/>
-    <col min="10499" max="10499" width="27" style="1" customWidth="1"/>
-    <col min="10500" max="10752" width="11" style="1"/>
-    <col min="10753" max="10753" width="35.125" style="1" customWidth="1"/>
-    <col min="10754" max="10754" width="33.375" style="1" customWidth="1"/>
-    <col min="10755" max="10755" width="27" style="1" customWidth="1"/>
-    <col min="10756" max="11008" width="11" style="1"/>
-    <col min="11009" max="11009" width="35.125" style="1" customWidth="1"/>
-    <col min="11010" max="11010" width="33.375" style="1" customWidth="1"/>
-    <col min="11011" max="11011" width="27" style="1" customWidth="1"/>
-    <col min="11012" max="11264" width="11" style="1"/>
-    <col min="11265" max="11265" width="35.125" style="1" customWidth="1"/>
-    <col min="11266" max="11266" width="33.375" style="1" customWidth="1"/>
-    <col min="11267" max="11267" width="27" style="1" customWidth="1"/>
-    <col min="11268" max="11520" width="11" style="1"/>
-    <col min="11521" max="11521" width="35.125" style="1" customWidth="1"/>
-    <col min="11522" max="11522" width="33.375" style="1" customWidth="1"/>
-    <col min="11523" max="11523" width="27" style="1" customWidth="1"/>
-    <col min="11524" max="11776" width="11" style="1"/>
-    <col min="11777" max="11777" width="35.125" style="1" customWidth="1"/>
-    <col min="11778" max="11778" width="33.375" style="1" customWidth="1"/>
-    <col min="11779" max="11779" width="27" style="1" customWidth="1"/>
-    <col min="11780" max="12032" width="11" style="1"/>
-    <col min="12033" max="12033" width="35.125" style="1" customWidth="1"/>
-    <col min="12034" max="12034" width="33.375" style="1" customWidth="1"/>
-    <col min="12035" max="12035" width="27" style="1" customWidth="1"/>
-    <col min="12036" max="12288" width="11" style="1"/>
-    <col min="12289" max="12289" width="35.125" style="1" customWidth="1"/>
-    <col min="12290" max="12290" width="33.375" style="1" customWidth="1"/>
-    <col min="12291" max="12291" width="27" style="1" customWidth="1"/>
-    <col min="12292" max="12544" width="11" style="1"/>
-    <col min="12545" max="12545" width="35.125" style="1" customWidth="1"/>
-    <col min="12546" max="12546" width="33.375" style="1" customWidth="1"/>
-    <col min="12547" max="12547" width="27" style="1" customWidth="1"/>
-    <col min="12548" max="12800" width="11" style="1"/>
-    <col min="12801" max="12801" width="35.125" style="1" customWidth="1"/>
-    <col min="12802" max="12802" width="33.375" style="1" customWidth="1"/>
-    <col min="12803" max="12803" width="27" style="1" customWidth="1"/>
-    <col min="12804" max="13056" width="11" style="1"/>
-    <col min="13057" max="13057" width="35.125" style="1" customWidth="1"/>
-    <col min="13058" max="13058" width="33.375" style="1" customWidth="1"/>
-    <col min="13059" max="13059" width="27" style="1" customWidth="1"/>
-    <col min="13060" max="13312" width="11" style="1"/>
-    <col min="13313" max="13313" width="35.125" style="1" customWidth="1"/>
-    <col min="13314" max="13314" width="33.375" style="1" customWidth="1"/>
-    <col min="13315" max="13315" width="27" style="1" customWidth="1"/>
-    <col min="13316" max="13568" width="11" style="1"/>
-    <col min="13569" max="13569" width="35.125" style="1" customWidth="1"/>
-    <col min="13570" max="13570" width="33.375" style="1" customWidth="1"/>
-    <col min="13571" max="13571" width="27" style="1" customWidth="1"/>
-    <col min="13572" max="13824" width="11" style="1"/>
-    <col min="13825" max="13825" width="35.125" style="1" customWidth="1"/>
-    <col min="13826" max="13826" width="33.375" style="1" customWidth="1"/>
-    <col min="13827" max="13827" width="27" style="1" customWidth="1"/>
-    <col min="13828" max="14080" width="11" style="1"/>
-    <col min="14081" max="14081" width="35.125" style="1" customWidth="1"/>
-    <col min="14082" max="14082" width="33.375" style="1" customWidth="1"/>
-    <col min="14083" max="14083" width="27" style="1" customWidth="1"/>
-    <col min="14084" max="14336" width="11" style="1"/>
-    <col min="14337" max="14337" width="35.125" style="1" customWidth="1"/>
-    <col min="14338" max="14338" width="33.375" style="1" customWidth="1"/>
-    <col min="14339" max="14339" width="27" style="1" customWidth="1"/>
-    <col min="14340" max="14592" width="11" style="1"/>
-    <col min="14593" max="14593" width="35.125" style="1" customWidth="1"/>
-    <col min="14594" max="14594" width="33.375" style="1" customWidth="1"/>
-    <col min="14595" max="14595" width="27" style="1" customWidth="1"/>
-    <col min="14596" max="14848" width="11" style="1"/>
-    <col min="14849" max="14849" width="35.125" style="1" customWidth="1"/>
-    <col min="14850" max="14850" width="33.375" style="1" customWidth="1"/>
-    <col min="14851" max="14851" width="27" style="1" customWidth="1"/>
-    <col min="14852" max="15104" width="11" style="1"/>
-    <col min="15105" max="15105" width="35.125" style="1" customWidth="1"/>
-    <col min="15106" max="15106" width="33.375" style="1" customWidth="1"/>
-    <col min="15107" max="15107" width="27" style="1" customWidth="1"/>
-    <col min="15108" max="15360" width="11" style="1"/>
-    <col min="15361" max="15361" width="35.125" style="1" customWidth="1"/>
-    <col min="15362" max="15362" width="33.375" style="1" customWidth="1"/>
-    <col min="15363" max="15363" width="27" style="1" customWidth="1"/>
-    <col min="15364" max="15616" width="11" style="1"/>
-    <col min="15617" max="15617" width="35.125" style="1" customWidth="1"/>
-    <col min="15618" max="15618" width="33.375" style="1" customWidth="1"/>
-    <col min="15619" max="15619" width="27" style="1" customWidth="1"/>
-    <col min="15620" max="15872" width="11" style="1"/>
-    <col min="15873" max="15873" width="35.125" style="1" customWidth="1"/>
-    <col min="15874" max="15874" width="33.375" style="1" customWidth="1"/>
-    <col min="15875" max="15875" width="27" style="1" customWidth="1"/>
-    <col min="15876" max="16128" width="11" style="1"/>
-    <col min="16129" max="16129" width="35.125" style="1" customWidth="1"/>
-    <col min="16130" max="16130" width="33.375" style="1" customWidth="1"/>
-    <col min="16131" max="16131" width="27" style="1" customWidth="1"/>
-    <col min="16132" max="16384" width="11" style="1"/>
+    <col min="1" max="1" width="23" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.625" style="2" customWidth="1"/>
+    <col min="5" max="256" width="11" style="1"/>
+    <col min="257" max="257" width="23" style="1" customWidth="1"/>
+    <col min="258" max="258" width="22" style="1" customWidth="1"/>
+    <col min="259" max="259" width="24.875" style="1" customWidth="1"/>
+    <col min="260" max="260" width="21.625" style="1" customWidth="1"/>
+    <col min="261" max="512" width="11" style="1"/>
+    <col min="513" max="513" width="23" style="1" customWidth="1"/>
+    <col min="514" max="514" width="22" style="1" customWidth="1"/>
+    <col min="515" max="515" width="24.875" style="1" customWidth="1"/>
+    <col min="516" max="516" width="21.625" style="1" customWidth="1"/>
+    <col min="517" max="768" width="11" style="1"/>
+    <col min="769" max="769" width="23" style="1" customWidth="1"/>
+    <col min="770" max="770" width="22" style="1" customWidth="1"/>
+    <col min="771" max="771" width="24.875" style="1" customWidth="1"/>
+    <col min="772" max="772" width="21.625" style="1" customWidth="1"/>
+    <col min="773" max="1024" width="11" style="1"/>
+    <col min="1025" max="1025" width="23" style="1" customWidth="1"/>
+    <col min="1026" max="1026" width="22" style="1" customWidth="1"/>
+    <col min="1027" max="1027" width="24.875" style="1" customWidth="1"/>
+    <col min="1028" max="1028" width="21.625" style="1" customWidth="1"/>
+    <col min="1029" max="1280" width="11" style="1"/>
+    <col min="1281" max="1281" width="23" style="1" customWidth="1"/>
+    <col min="1282" max="1282" width="22" style="1" customWidth="1"/>
+    <col min="1283" max="1283" width="24.875" style="1" customWidth="1"/>
+    <col min="1284" max="1284" width="21.625" style="1" customWidth="1"/>
+    <col min="1285" max="1536" width="11" style="1"/>
+    <col min="1537" max="1537" width="23" style="1" customWidth="1"/>
+    <col min="1538" max="1538" width="22" style="1" customWidth="1"/>
+    <col min="1539" max="1539" width="24.875" style="1" customWidth="1"/>
+    <col min="1540" max="1540" width="21.625" style="1" customWidth="1"/>
+    <col min="1541" max="1792" width="11" style="1"/>
+    <col min="1793" max="1793" width="23" style="1" customWidth="1"/>
+    <col min="1794" max="1794" width="22" style="1" customWidth="1"/>
+    <col min="1795" max="1795" width="24.875" style="1" customWidth="1"/>
+    <col min="1796" max="1796" width="21.625" style="1" customWidth="1"/>
+    <col min="1797" max="2048" width="11" style="1"/>
+    <col min="2049" max="2049" width="23" style="1" customWidth="1"/>
+    <col min="2050" max="2050" width="22" style="1" customWidth="1"/>
+    <col min="2051" max="2051" width="24.875" style="1" customWidth="1"/>
+    <col min="2052" max="2052" width="21.625" style="1" customWidth="1"/>
+    <col min="2053" max="2304" width="11" style="1"/>
+    <col min="2305" max="2305" width="23" style="1" customWidth="1"/>
+    <col min="2306" max="2306" width="22" style="1" customWidth="1"/>
+    <col min="2307" max="2307" width="24.875" style="1" customWidth="1"/>
+    <col min="2308" max="2308" width="21.625" style="1" customWidth="1"/>
+    <col min="2309" max="2560" width="11" style="1"/>
+    <col min="2561" max="2561" width="23" style="1" customWidth="1"/>
+    <col min="2562" max="2562" width="22" style="1" customWidth="1"/>
+    <col min="2563" max="2563" width="24.875" style="1" customWidth="1"/>
+    <col min="2564" max="2564" width="21.625" style="1" customWidth="1"/>
+    <col min="2565" max="2816" width="11" style="1"/>
+    <col min="2817" max="2817" width="23" style="1" customWidth="1"/>
+    <col min="2818" max="2818" width="22" style="1" customWidth="1"/>
+    <col min="2819" max="2819" width="24.875" style="1" customWidth="1"/>
+    <col min="2820" max="2820" width="21.625" style="1" customWidth="1"/>
+    <col min="2821" max="3072" width="11" style="1"/>
+    <col min="3073" max="3073" width="23" style="1" customWidth="1"/>
+    <col min="3074" max="3074" width="22" style="1" customWidth="1"/>
+    <col min="3075" max="3075" width="24.875" style="1" customWidth="1"/>
+    <col min="3076" max="3076" width="21.625" style="1" customWidth="1"/>
+    <col min="3077" max="3328" width="11" style="1"/>
+    <col min="3329" max="3329" width="23" style="1" customWidth="1"/>
+    <col min="3330" max="3330" width="22" style="1" customWidth="1"/>
+    <col min="3331" max="3331" width="24.875" style="1" customWidth="1"/>
+    <col min="3332" max="3332" width="21.625" style="1" customWidth="1"/>
+    <col min="3333" max="3584" width="11" style="1"/>
+    <col min="3585" max="3585" width="23" style="1" customWidth="1"/>
+    <col min="3586" max="3586" width="22" style="1" customWidth="1"/>
+    <col min="3587" max="3587" width="24.875" style="1" customWidth="1"/>
+    <col min="3588" max="3588" width="21.625" style="1" customWidth="1"/>
+    <col min="3589" max="3840" width="11" style="1"/>
+    <col min="3841" max="3841" width="23" style="1" customWidth="1"/>
+    <col min="3842" max="3842" width="22" style="1" customWidth="1"/>
+    <col min="3843" max="3843" width="24.875" style="1" customWidth="1"/>
+    <col min="3844" max="3844" width="21.625" style="1" customWidth="1"/>
+    <col min="3845" max="4096" width="11" style="1"/>
+    <col min="4097" max="4097" width="23" style="1" customWidth="1"/>
+    <col min="4098" max="4098" width="22" style="1" customWidth="1"/>
+    <col min="4099" max="4099" width="24.875" style="1" customWidth="1"/>
+    <col min="4100" max="4100" width="21.625" style="1" customWidth="1"/>
+    <col min="4101" max="4352" width="11" style="1"/>
+    <col min="4353" max="4353" width="23" style="1" customWidth="1"/>
+    <col min="4354" max="4354" width="22" style="1" customWidth="1"/>
+    <col min="4355" max="4355" width="24.875" style="1" customWidth="1"/>
+    <col min="4356" max="4356" width="21.625" style="1" customWidth="1"/>
+    <col min="4357" max="4608" width="11" style="1"/>
+    <col min="4609" max="4609" width="23" style="1" customWidth="1"/>
+    <col min="4610" max="4610" width="22" style="1" customWidth="1"/>
+    <col min="4611" max="4611" width="24.875" style="1" customWidth="1"/>
+    <col min="4612" max="4612" width="21.625" style="1" customWidth="1"/>
+    <col min="4613" max="4864" width="11" style="1"/>
+    <col min="4865" max="4865" width="23" style="1" customWidth="1"/>
+    <col min="4866" max="4866" width="22" style="1" customWidth="1"/>
+    <col min="4867" max="4867" width="24.875" style="1" customWidth="1"/>
+    <col min="4868" max="4868" width="21.625" style="1" customWidth="1"/>
+    <col min="4869" max="5120" width="11" style="1"/>
+    <col min="5121" max="5121" width="23" style="1" customWidth="1"/>
+    <col min="5122" max="5122" width="22" style="1" customWidth="1"/>
+    <col min="5123" max="5123" width="24.875" style="1" customWidth="1"/>
+    <col min="5124" max="5124" width="21.625" style="1" customWidth="1"/>
+    <col min="5125" max="5376" width="11" style="1"/>
+    <col min="5377" max="5377" width="23" style="1" customWidth="1"/>
+    <col min="5378" max="5378" width="22" style="1" customWidth="1"/>
+    <col min="5379" max="5379" width="24.875" style="1" customWidth="1"/>
+    <col min="5380" max="5380" width="21.625" style="1" customWidth="1"/>
+    <col min="5381" max="5632" width="11" style="1"/>
+    <col min="5633" max="5633" width="23" style="1" customWidth="1"/>
+    <col min="5634" max="5634" width="22" style="1" customWidth="1"/>
+    <col min="5635" max="5635" width="24.875" style="1" customWidth="1"/>
+    <col min="5636" max="5636" width="21.625" style="1" customWidth="1"/>
+    <col min="5637" max="5888" width="11" style="1"/>
+    <col min="5889" max="5889" width="23" style="1" customWidth="1"/>
+    <col min="5890" max="5890" width="22" style="1" customWidth="1"/>
+    <col min="5891" max="5891" width="24.875" style="1" customWidth="1"/>
+    <col min="5892" max="5892" width="21.625" style="1" customWidth="1"/>
+    <col min="5893" max="6144" width="11" style="1"/>
+    <col min="6145" max="6145" width="23" style="1" customWidth="1"/>
+    <col min="6146" max="6146" width="22" style="1" customWidth="1"/>
+    <col min="6147" max="6147" width="24.875" style="1" customWidth="1"/>
+    <col min="6148" max="6148" width="21.625" style="1" customWidth="1"/>
+    <col min="6149" max="6400" width="11" style="1"/>
+    <col min="6401" max="6401" width="23" style="1" customWidth="1"/>
+    <col min="6402" max="6402" width="22" style="1" customWidth="1"/>
+    <col min="6403" max="6403" width="24.875" style="1" customWidth="1"/>
+    <col min="6404" max="6404" width="21.625" style="1" customWidth="1"/>
+    <col min="6405" max="6656" width="11" style="1"/>
+    <col min="6657" max="6657" width="23" style="1" customWidth="1"/>
+    <col min="6658" max="6658" width="22" style="1" customWidth="1"/>
+    <col min="6659" max="6659" width="24.875" style="1" customWidth="1"/>
+    <col min="6660" max="6660" width="21.625" style="1" customWidth="1"/>
+    <col min="6661" max="6912" width="11" style="1"/>
+    <col min="6913" max="6913" width="23" style="1" customWidth="1"/>
+    <col min="6914" max="6914" width="22" style="1" customWidth="1"/>
+    <col min="6915" max="6915" width="24.875" style="1" customWidth="1"/>
+    <col min="6916" max="6916" width="21.625" style="1" customWidth="1"/>
+    <col min="6917" max="7168" width="11" style="1"/>
+    <col min="7169" max="7169" width="23" style="1" customWidth="1"/>
+    <col min="7170" max="7170" width="22" style="1" customWidth="1"/>
+    <col min="7171" max="7171" width="24.875" style="1" customWidth="1"/>
+    <col min="7172" max="7172" width="21.625" style="1" customWidth="1"/>
+    <col min="7173" max="7424" width="11" style="1"/>
+    <col min="7425" max="7425" width="23" style="1" customWidth="1"/>
+    <col min="7426" max="7426" width="22" style="1" customWidth="1"/>
+    <col min="7427" max="7427" width="24.875" style="1" customWidth="1"/>
+    <col min="7428" max="7428" width="21.625" style="1" customWidth="1"/>
+    <col min="7429" max="7680" width="11" style="1"/>
+    <col min="7681" max="7681" width="23" style="1" customWidth="1"/>
+    <col min="7682" max="7682" width="22" style="1" customWidth="1"/>
+    <col min="7683" max="7683" width="24.875" style="1" customWidth="1"/>
+    <col min="7684" max="7684" width="21.625" style="1" customWidth="1"/>
+    <col min="7685" max="7936" width="11" style="1"/>
+    <col min="7937" max="7937" width="23" style="1" customWidth="1"/>
+    <col min="7938" max="7938" width="22" style="1" customWidth="1"/>
+    <col min="7939" max="7939" width="24.875" style="1" customWidth="1"/>
+    <col min="7940" max="7940" width="21.625" style="1" customWidth="1"/>
+    <col min="7941" max="8192" width="11" style="1"/>
+    <col min="8193" max="8193" width="23" style="1" customWidth="1"/>
+    <col min="8194" max="8194" width="22" style="1" customWidth="1"/>
+    <col min="8195" max="8195" width="24.875" style="1" customWidth="1"/>
+    <col min="8196" max="8196" width="21.625" style="1" customWidth="1"/>
+    <col min="8197" max="8448" width="11" style="1"/>
+    <col min="8449" max="8449" width="23" style="1" customWidth="1"/>
+    <col min="8450" max="8450" width="22" style="1" customWidth="1"/>
+    <col min="8451" max="8451" width="24.875" style="1" customWidth="1"/>
+    <col min="8452" max="8452" width="21.625" style="1" customWidth="1"/>
+    <col min="8453" max="8704" width="11" style="1"/>
+    <col min="8705" max="8705" width="23" style="1" customWidth="1"/>
+    <col min="8706" max="8706" width="22" style="1" customWidth="1"/>
+    <col min="8707" max="8707" width="24.875" style="1" customWidth="1"/>
+    <col min="8708" max="8708" width="21.625" style="1" customWidth="1"/>
+    <col min="8709" max="8960" width="11" style="1"/>
+    <col min="8961" max="8961" width="23" style="1" customWidth="1"/>
+    <col min="8962" max="8962" width="22" style="1" customWidth="1"/>
+    <col min="8963" max="8963" width="24.875" style="1" customWidth="1"/>
+    <col min="8964" max="8964" width="21.625" style="1" customWidth="1"/>
+    <col min="8965" max="9216" width="11" style="1"/>
+    <col min="9217" max="9217" width="23" style="1" customWidth="1"/>
+    <col min="9218" max="9218" width="22" style="1" customWidth="1"/>
+    <col min="9219" max="9219" width="24.875" style="1" customWidth="1"/>
+    <col min="9220" max="9220" width="21.625" style="1" customWidth="1"/>
+    <col min="9221" max="9472" width="11" style="1"/>
+    <col min="9473" max="9473" width="23" style="1" customWidth="1"/>
+    <col min="9474" max="9474" width="22" style="1" customWidth="1"/>
+    <col min="9475" max="9475" width="24.875" style="1" customWidth="1"/>
+    <col min="9476" max="9476" width="21.625" style="1" customWidth="1"/>
+    <col min="9477" max="9728" width="11" style="1"/>
+    <col min="9729" max="9729" width="23" style="1" customWidth="1"/>
+    <col min="9730" max="9730" width="22" style="1" customWidth="1"/>
+    <col min="9731" max="9731" width="24.875" style="1" customWidth="1"/>
+    <col min="9732" max="9732" width="21.625" style="1" customWidth="1"/>
+    <col min="9733" max="9984" width="11" style="1"/>
+    <col min="9985" max="9985" width="23" style="1" customWidth="1"/>
+    <col min="9986" max="9986" width="22" style="1" customWidth="1"/>
+    <col min="9987" max="9987" width="24.875" style="1" customWidth="1"/>
+    <col min="9988" max="9988" width="21.625" style="1" customWidth="1"/>
+    <col min="9989" max="10240" width="11" style="1"/>
+    <col min="10241" max="10241" width="23" style="1" customWidth="1"/>
+    <col min="10242" max="10242" width="22" style="1" customWidth="1"/>
+    <col min="10243" max="10243" width="24.875" style="1" customWidth="1"/>
+    <col min="10244" max="10244" width="21.625" style="1" customWidth="1"/>
+    <col min="10245" max="10496" width="11" style="1"/>
+    <col min="10497" max="10497" width="23" style="1" customWidth="1"/>
+    <col min="10498" max="10498" width="22" style="1" customWidth="1"/>
+    <col min="10499" max="10499" width="24.875" style="1" customWidth="1"/>
+    <col min="10500" max="10500" width="21.625" style="1" customWidth="1"/>
+    <col min="10501" max="10752" width="11" style="1"/>
+    <col min="10753" max="10753" width="23" style="1" customWidth="1"/>
+    <col min="10754" max="10754" width="22" style="1" customWidth="1"/>
+    <col min="10755" max="10755" width="24.875" style="1" customWidth="1"/>
+    <col min="10756" max="10756" width="21.625" style="1" customWidth="1"/>
+    <col min="10757" max="11008" width="11" style="1"/>
+    <col min="11009" max="11009" width="23" style="1" customWidth="1"/>
+    <col min="11010" max="11010" width="22" style="1" customWidth="1"/>
+    <col min="11011" max="11011" width="24.875" style="1" customWidth="1"/>
+    <col min="11012" max="11012" width="21.625" style="1" customWidth="1"/>
+    <col min="11013" max="11264" width="11" style="1"/>
+    <col min="11265" max="11265" width="23" style="1" customWidth="1"/>
+    <col min="11266" max="11266" width="22" style="1" customWidth="1"/>
+    <col min="11267" max="11267" width="24.875" style="1" customWidth="1"/>
+    <col min="11268" max="11268" width="21.625" style="1" customWidth="1"/>
+    <col min="11269" max="11520" width="11" style="1"/>
+    <col min="11521" max="11521" width="23" style="1" customWidth="1"/>
+    <col min="11522" max="11522" width="22" style="1" customWidth="1"/>
+    <col min="11523" max="11523" width="24.875" style="1" customWidth="1"/>
+    <col min="11524" max="11524" width="21.625" style="1" customWidth="1"/>
+    <col min="11525" max="11776" width="11" style="1"/>
+    <col min="11777" max="11777" width="23" style="1" customWidth="1"/>
+    <col min="11778" max="11778" width="22" style="1" customWidth="1"/>
+    <col min="11779" max="11779" width="24.875" style="1" customWidth="1"/>
+    <col min="11780" max="11780" width="21.625" style="1" customWidth="1"/>
+    <col min="11781" max="12032" width="11" style="1"/>
+    <col min="12033" max="12033" width="23" style="1" customWidth="1"/>
+    <col min="12034" max="12034" width="22" style="1" customWidth="1"/>
+    <col min="12035" max="12035" width="24.875" style="1" customWidth="1"/>
+    <col min="12036" max="12036" width="21.625" style="1" customWidth="1"/>
+    <col min="12037" max="12288" width="11" style="1"/>
+    <col min="12289" max="12289" width="23" style="1" customWidth="1"/>
+    <col min="12290" max="12290" width="22" style="1" customWidth="1"/>
+    <col min="12291" max="12291" width="24.875" style="1" customWidth="1"/>
+    <col min="12292" max="12292" width="21.625" style="1" customWidth="1"/>
+    <col min="12293" max="12544" width="11" style="1"/>
+    <col min="12545" max="12545" width="23" style="1" customWidth="1"/>
+    <col min="12546" max="12546" width="22" style="1" customWidth="1"/>
+    <col min="12547" max="12547" width="24.875" style="1" customWidth="1"/>
+    <col min="12548" max="12548" width="21.625" style="1" customWidth="1"/>
+    <col min="12549" max="12800" width="11" style="1"/>
+    <col min="12801" max="12801" width="23" style="1" customWidth="1"/>
+    <col min="12802" max="12802" width="22" style="1" customWidth="1"/>
+    <col min="12803" max="12803" width="24.875" style="1" customWidth="1"/>
+    <col min="12804" max="12804" width="21.625" style="1" customWidth="1"/>
+    <col min="12805" max="13056" width="11" style="1"/>
+    <col min="13057" max="13057" width="23" style="1" customWidth="1"/>
+    <col min="13058" max="13058" width="22" style="1" customWidth="1"/>
+    <col min="13059" max="13059" width="24.875" style="1" customWidth="1"/>
+    <col min="13060" max="13060" width="21.625" style="1" customWidth="1"/>
+    <col min="13061" max="13312" width="11" style="1"/>
+    <col min="13313" max="13313" width="23" style="1" customWidth="1"/>
+    <col min="13314" max="13314" width="22" style="1" customWidth="1"/>
+    <col min="13315" max="13315" width="24.875" style="1" customWidth="1"/>
+    <col min="13316" max="13316" width="21.625" style="1" customWidth="1"/>
+    <col min="13317" max="13568" width="11" style="1"/>
+    <col min="13569" max="13569" width="23" style="1" customWidth="1"/>
+    <col min="13570" max="13570" width="22" style="1" customWidth="1"/>
+    <col min="13571" max="13571" width="24.875" style="1" customWidth="1"/>
+    <col min="13572" max="13572" width="21.625" style="1" customWidth="1"/>
+    <col min="13573" max="13824" width="11" style="1"/>
+    <col min="13825" max="13825" width="23" style="1" customWidth="1"/>
+    <col min="13826" max="13826" width="22" style="1" customWidth="1"/>
+    <col min="13827" max="13827" width="24.875" style="1" customWidth="1"/>
+    <col min="13828" max="13828" width="21.625" style="1" customWidth="1"/>
+    <col min="13829" max="14080" width="11" style="1"/>
+    <col min="14081" max="14081" width="23" style="1" customWidth="1"/>
+    <col min="14082" max="14082" width="22" style="1" customWidth="1"/>
+    <col min="14083" max="14083" width="24.875" style="1" customWidth="1"/>
+    <col min="14084" max="14084" width="21.625" style="1" customWidth="1"/>
+    <col min="14085" max="14336" width="11" style="1"/>
+    <col min="14337" max="14337" width="23" style="1" customWidth="1"/>
+    <col min="14338" max="14338" width="22" style="1" customWidth="1"/>
+    <col min="14339" max="14339" width="24.875" style="1" customWidth="1"/>
+    <col min="14340" max="14340" width="21.625" style="1" customWidth="1"/>
+    <col min="14341" max="14592" width="11" style="1"/>
+    <col min="14593" max="14593" width="23" style="1" customWidth="1"/>
+    <col min="14594" max="14594" width="22" style="1" customWidth="1"/>
+    <col min="14595" max="14595" width="24.875" style="1" customWidth="1"/>
+    <col min="14596" max="14596" width="21.625" style="1" customWidth="1"/>
+    <col min="14597" max="14848" width="11" style="1"/>
+    <col min="14849" max="14849" width="23" style="1" customWidth="1"/>
+    <col min="14850" max="14850" width="22" style="1" customWidth="1"/>
+    <col min="14851" max="14851" width="24.875" style="1" customWidth="1"/>
+    <col min="14852" max="14852" width="21.625" style="1" customWidth="1"/>
+    <col min="14853" max="15104" width="11" style="1"/>
+    <col min="15105" max="15105" width="23" style="1" customWidth="1"/>
+    <col min="15106" max="15106" width="22" style="1" customWidth="1"/>
+    <col min="15107" max="15107" width="24.875" style="1" customWidth="1"/>
+    <col min="15108" max="15108" width="21.625" style="1" customWidth="1"/>
+    <col min="15109" max="15360" width="11" style="1"/>
+    <col min="15361" max="15361" width="23" style="1" customWidth="1"/>
+    <col min="15362" max="15362" width="22" style="1" customWidth="1"/>
+    <col min="15363" max="15363" width="24.875" style="1" customWidth="1"/>
+    <col min="15364" max="15364" width="21.625" style="1" customWidth="1"/>
+    <col min="15365" max="15616" width="11" style="1"/>
+    <col min="15617" max="15617" width="23" style="1" customWidth="1"/>
+    <col min="15618" max="15618" width="22" style="1" customWidth="1"/>
+    <col min="15619" max="15619" width="24.875" style="1" customWidth="1"/>
+    <col min="15620" max="15620" width="21.625" style="1" customWidth="1"/>
+    <col min="15621" max="15872" width="11" style="1"/>
+    <col min="15873" max="15873" width="23" style="1" customWidth="1"/>
+    <col min="15874" max="15874" width="22" style="1" customWidth="1"/>
+    <col min="15875" max="15875" width="24.875" style="1" customWidth="1"/>
+    <col min="15876" max="15876" width="21.625" style="1" customWidth="1"/>
+    <col min="15877" max="16128" width="11" style="1"/>
+    <col min="16129" max="16129" width="23" style="1" customWidth="1"/>
+    <col min="16130" max="16130" width="22" style="1" customWidth="1"/>
+    <col min="16131" max="16131" width="24.875" style="1" customWidth="1"/>
+    <col min="16132" max="16132" width="21.625" style="1" customWidth="1"/>
+    <col min="16133" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="22.5" x14ac:dyDescent="0.15">
@@ -1058,210 +1098,243 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>31</v>
+      <c r="B4" s="6" t="e">
+        <f>SUM(B5,B8,B11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C4" s="6" t="e">
+        <f>SUM(C5,C8,C11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D4" s="6" t="e">
+        <f>SUM(D5,D8,D11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-    </row>
-    <row r="6" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+      <c r="B5" s="6" t="e">
+        <f>SUM(B6,-B7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" s="10" t="e">
+        <f>C6-C7</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D5" s="10" t="e">
+        <f>D6-D7</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="B8" s="10" t="e">
+        <f>B9-B10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="10" t="e">
+        <f>C9-C10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D8" s="10" t="e">
+        <f>D9-D10</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="B11" s="10" t="e">
+        <f>B12-B13</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" s="10" t="e">
+        <f>C12-C13</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D11" s="10" t="e">
+        <f>D12-D13</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>67</v>
+      <c r="B19" s="6">
+        <f>SUM(B20,B21,B22)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="6">
+        <f>SUM(C20,C21,C22)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <f>SUM(D20,D21,D22)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="27" x14ac:dyDescent="0.15">
@@ -1269,69 +1342,55 @@
         <v>22</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="27" x14ac:dyDescent="0.15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="40.5" x14ac:dyDescent="0.15">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="27" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="27" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/hxprofit/HXProfit.xlsx
+++ b/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/hxprofit/HXProfit.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20373"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC589F52-ED90-47EE-B8CB-E880C0ECE4AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A647C5-FA55-4CAD-B8EF-589D9C83D55B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,8 +236,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -370,7 +371,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -393,13 +394,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1069,20 +1073,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
@@ -1102,16 +1106,16 @@
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="e">
-        <f>SUM(B5,B8,B11)</f>
+      <c r="B4" s="8" t="e">
+        <f>B5+B8+B11</f>
         <v>#VALUE!</v>
       </c>
       <c r="C4" s="6" t="e">
-        <f>SUM(C5,C8,C11)</f>
+        <f>C5+C8+C11</f>
         <v>#VALUE!</v>
       </c>
       <c r="D4" s="6" t="e">
-        <f>SUM(D5,D8,D11)</f>
+        <f>D5+D8+D11</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1120,14 +1124,14 @@
         <v>7</v>
       </c>
       <c r="B5" s="6" t="e">
-        <f>SUM(B6,-B7)</f>
+        <f>B6-B7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C5" s="10" t="e">
+      <c r="C5" s="8" t="e">
         <f>C6-C7</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D5" s="10" t="e">
+      <c r="D5" s="8" t="e">
         <f>D6-D7</f>
         <v>#VALUE!</v>
       </c>
@@ -1136,13 +1140,13 @@
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="11" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1150,13 +1154,13 @@
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="11" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1164,15 +1168,15 @@
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="10" t="e">
+      <c r="B8" s="8" t="e">
         <f>B9-B10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C8" s="10" t="e">
+      <c r="C8" s="8" t="e">
         <f>C9-C10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D8" s="10" t="e">
+      <c r="D8" s="8" t="e">
         <f>D9-D10</f>
         <v>#VALUE!</v>
       </c>
@@ -1209,15 +1213,15 @@
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="10" t="e">
+      <c r="B11" s="8" t="e">
         <f>B12-B13</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C11" s="10" t="e">
+      <c r="C11" s="8" t="e">
         <f>C12-C13</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D11" s="10" t="e">
+      <c r="D11" s="8" t="e">
         <f>D12-D13</f>
         <v>#VALUE!</v>
       </c>
@@ -1324,17 +1328,17 @@
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="6">
-        <f>SUM(B20,B21,B22)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="6">
-        <f>SUM(C20,C21,C22)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="6">
-        <f>SUM(D20,D21,D22)</f>
-        <v>0</v>
+      <c r="B19" s="8" t="e">
+        <f>B20+B21+B22</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C19" s="8" t="e">
+        <f>C20+C21+C22</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D19" s="8" t="e">
+        <f>D20+D21+D22</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="27" x14ac:dyDescent="0.15">
